--- a/tracking_2.xlsx
+++ b/tracking_2.xlsx
@@ -1,489 +1,98 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Export Summary" sheetId="1" r:id="rId4"/>
-    <sheet name="BL Input" sheetId="2" r:id="rId5"/>
-    <sheet name="Tracking Results" sheetId="3" r:id="rId6"/>
+    <sheet name="Export Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BL Input" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tracking Results" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tracking Results'!$A$1:$J$1</definedName>
+  </definedNames>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="127">
-  <si>
-    <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
-  </si>
-  <si>
-    <t>Numbers Sheet Name</t>
-  </si>
-  <si>
-    <t>Numbers Table Name</t>
-  </si>
-  <si>
-    <t>Excel Worksheet Name</t>
-  </si>
-  <si>
-    <t>Export Summary</t>
-  </si>
-  <si>
-    <t>Table 1</t>
-  </si>
-  <si>
-    <t>BL Input</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="12"/>
-        <color indexed="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>BL Input</t>
-    </r>
-  </si>
-  <si>
-    <t>Tracking Results</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <u val="single"/>
-        <sz val="12"/>
-        <color indexed="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t>Tracking Results</t>
-    </r>
-  </si>
-  <si>
-    <t>BL No</t>
-  </si>
-  <si>
-    <t>Shipping Line</t>
-  </si>
-  <si>
-    <t>LPL1488455</t>
-  </si>
-  <si>
-    <t>CMA</t>
-  </si>
-  <si>
-    <t>LPL1487732</t>
-  </si>
-  <si>
-    <t>DBA0396239</t>
-  </si>
-  <si>
-    <t>LPL1489111</t>
-  </si>
-  <si>
-    <t>LPL1489079</t>
-  </si>
-  <si>
-    <t>SIJ0562405</t>
-  </si>
-  <si>
-    <t>DBA0403331A</t>
-  </si>
-  <si>
-    <t>SNG0495243</t>
-  </si>
-  <si>
-    <t>POL</t>
-  </si>
-  <si>
-    <t>POD</t>
-  </si>
-  <si>
-    <t>Container No</t>
-  </si>
-  <si>
-    <t>Vessel</t>
-  </si>
-  <si>
-    <t>ATA</t>
-  </si>
-  <si>
-    <t>Latest Status</t>
-  </si>
-  <si>
-    <t>Last Updated</t>
-  </si>
-  <si>
-    <t>6439251269</t>
-  </si>
-  <si>
-    <t>Cosco</t>
-  </si>
-  <si>
-    <t>CSNU6515981</t>
-  </si>
-  <si>
-    <t>EVER ACME</t>
-  </si>
-  <si>
-    <t>2026-03-06 06:00:00 IST</t>
-  </si>
-  <si>
-    <t>2026-03-08 15:20:00 IST</t>
-  </si>
-  <si>
-    <t>Transport Completed</t>
-  </si>
-  <si>
-    <t>2026-06-03 12:36</t>
-  </si>
-  <si>
-    <t>6439658390</t>
-  </si>
-  <si>
-    <t>No data</t>
-  </si>
-  <si>
-    <t>2026-03-08 06:33:00 IST</t>
-  </si>
-  <si>
-    <t>6449537710</t>
-  </si>
-  <si>
-    <t>CSGU6346619</t>
-  </si>
-  <si>
-    <t>TEXAS TRIUMPH</t>
-  </si>
-  <si>
-    <t>2026-05-28 03:30:00 IST</t>
-  </si>
-  <si>
-    <t>2026-05-29 04:43:00 IST</t>
-  </si>
-  <si>
-    <t>Empty Return</t>
-  </si>
-  <si>
-    <t>2026-06-03 12:38</t>
-  </si>
-  <si>
-    <t>6450334910</t>
-  </si>
-  <si>
-    <t>CSGU6674264</t>
-  </si>
-  <si>
-    <t>UAFL RACER</t>
-  </si>
-  <si>
-    <t>2026-06-30 20:00:00 IST</t>
-  </si>
-  <si>
-    <t>2026-07-04 00:00:00 IST</t>
-  </si>
-  <si>
-    <t>Discharged at T/S Port</t>
-  </si>
-  <si>
-    <t>2026-06-03 12:39</t>
-  </si>
-  <si>
-    <t>6500092990</t>
-  </si>
-  <si>
-    <t>BEAU5564910</t>
-  </si>
-  <si>
-    <t>CMA CGM COLUMBIA</t>
-  </si>
-  <si>
-    <t>2026-06-19 12:30:00 IST</t>
-  </si>
-  <si>
-    <t>2026-06-20 00:00:00 IST</t>
-  </si>
-  <si>
-    <t>268533123</t>
-  </si>
-  <si>
-    <t>MAERSK</t>
-  </si>
-  <si>
-    <t>BARCELONA</t>
-  </si>
-  <si>
-    <t>JAWAHARLAL NEHRU</t>
-  </si>
-  <si>
-    <t>CAAU5397306</t>
-  </si>
-  <si>
-    <t>Discharge</t>
-  </si>
-  <si>
-    <t>Discharge • COLOMBO, SRI LANKA • 27 May 2026</t>
-  </si>
-  <si>
-    <t>2026-06-03 14:14</t>
-  </si>
-  <si>
-    <t>269381946</t>
-  </si>
-  <si>
-    <t>ZAGREB</t>
-  </si>
-  <si>
-    <t>HAZIRA</t>
-  </si>
-  <si>
-    <t>MRKU4225082</t>
-  </si>
-  <si>
-    <t>Discharge • PORT TANGIER MEDITERRANEE, MOROCCO • 16 May 2026</t>
-  </si>
-  <si>
-    <t>2026-06-03 14:17</t>
-  </si>
-  <si>
-    <t>269383957</t>
-  </si>
-  <si>
-    <t>DURBAN</t>
-  </si>
-  <si>
-    <t>TUTICORIN</t>
-  </si>
-  <si>
-    <t>FFAU2279258</t>
-  </si>
-  <si>
-    <t>Vessel departure</t>
-  </si>
-  <si>
-    <t>Vessel departure • MUNDRA, INDIA • 31 May 2026</t>
-  </si>
-  <si>
-    <t>267399967</t>
-  </si>
-  <si>
-    <t>ASHDOD</t>
-  </si>
-  <si>
-    <t>GAOU7118850</t>
-  </si>
-  <si>
-    <t>Empty container return</t>
-  </si>
-  <si>
-    <t>Empty container return • Tuticorin, India • 22 May 2026</t>
-  </si>
-  <si>
-    <t>269234530</t>
-  </si>
-  <si>
-    <t>TLLU5276111</t>
-  </si>
-  <si>
-    <t>269234219</t>
-  </si>
-  <si>
-    <t>MRSU4482165</t>
-  </si>
-  <si>
-    <t>Discharge • MUNDRA, INDIA • 12 May 2026</t>
-  </si>
-  <si>
-    <t>2026-06-03 14:18</t>
-  </si>
-  <si>
-    <t>MEDUGR867656</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>Sydney, AU</t>
-  </si>
-  <si>
-    <t>Tuticorin, IN</t>
-  </si>
-  <si>
-    <t>FFAU2577550</t>
-  </si>
-  <si>
-    <t>22/05/2026</t>
-  </si>
-  <si>
-    <t>Import Positioning In • Tuticorin, IN • 22/05/2026</t>
-  </si>
-  <si>
-    <t>2026-06-03 16:36</t>
-  </si>
-  <si>
-    <t>MEDURE451006</t>
-  </si>
-  <si>
-    <t>Liverpool, GB</t>
-  </si>
-  <si>
-    <t>Hazira Port/Surat, IN</t>
-  </si>
-  <si>
-    <t>MSBU6848060</t>
-  </si>
-  <si>
-    <t>02/06/2026</t>
-  </si>
-  <si>
-    <t>Empty received at CY • Hazira Port/Surat, IN • 02/06/2026</t>
-  </si>
-  <si>
-    <t>2026-06-03 16:34</t>
-  </si>
-  <si>
-    <t>MEDUBF405808</t>
-  </si>
-  <si>
-    <t>Belfast, GB</t>
-  </si>
-  <si>
-    <t>Nhava Sheva, IN</t>
-  </si>
-  <si>
-    <t>MSDU7055448</t>
-  </si>
-  <si>
-    <t>11/05/2026</t>
-  </si>
-  <si>
-    <t>Empty received at CY • Nhava Sheva, IN • 11/05/2026</t>
-  </si>
-  <si>
-    <t>MEDUK9740334</t>
-  </si>
-  <si>
-    <t>Gioia Tauro, IT</t>
-  </si>
-  <si>
-    <t>CAIU7128171</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>Empty received at CY • Hazira Port/Surat, IN • 31/03/2026</t>
-  </si>
-  <si>
-    <t>2026-06-03 16:35</t>
-  </si>
-  <si>
-    <t>FELIXSTOWE (GB)</t>
-  </si>
-  <si>
-    <t>TUTICORIN (IN)</t>
-  </si>
-  <si>
-    <t>CMAU8991493</t>
-  </si>
-  <si>
-    <t>Monday, 16-MAR-2026 12:21 PM</t>
-  </si>
-  <si>
-    <t>TUTICORIN
-CCIS GOLDEN HORN CONTAINER SERVICE</t>
-  </si>
-  <si>
-    <t>2026-06-03 16:51</t>
-  </si>
-  <si>
-    <t>ECMU5181172</t>
-  </si>
-  <si>
-    <t>Wednesday, 01-APR-2026 11:01 PM</t>
-  </si>
-  <si>
-    <t>2026-06-03 16:54</t>
-  </si>
-  <si>
-    <t>ECMU5145663</t>
-  </si>
-  <si>
-    <t>2026-06-03 16:55</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
-  </numFmts>
-  <fonts count="11">
+  <numFmts count="0"/>
+  <fonts count="13">
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="14"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Helvetica Neue"/>
+      <color indexed="8"/>
       <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="11"/>
+      <sz val="12"/>
       <u val="single"/>
-      <sz val="12"/>
-      <color indexed="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <color indexed="8"/>
       <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+      <color indexed="12"/>
       <sz val="10"/>
-      <color indexed="12"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color indexed="8"/>
       <sz val="9"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+      <color indexed="18"/>
       <sz val="9"/>
-      <color indexed="18"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <name val="Arial"/>
       <b val="1"/>
+      <color indexed="20"/>
       <sz val="9"/>
-      <color indexed="20"/>
+    </font>
+    <font>
       <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -530,8 +139,18 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -760,172 +379,201 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellXfs count="57">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="6" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="7" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="7" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="8" borderId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="10" fillId="8" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="ff000000"/>
@@ -2010,834 +1658,1475 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="1" max="1" width="2" style="6" customWidth="1"/>
-    <col min="2" max="4" width="30.5547" customWidth="1"/>
-    <col min="2" max="2" width="30.5" style="6" customWidth="1"/>
-    <col min="3" max="3" width="30.5" style="6" customWidth="1"/>
-    <col min="4" max="4" width="30.5" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10" style="6" customWidth="1"/>
-    <col min="6" max="16384" width="10" style="6" customWidth="1"/>
+    <col width="2" customWidth="1" style="38" min="1" max="1"/>
+    <col width="30.5" customWidth="1" style="38" min="2" max="2"/>
+    <col width="30.5" customWidth="1" style="38" min="3" max="3"/>
+    <col width="30.5" customWidth="1" style="38" min="4" max="4"/>
+    <col width="10" customWidth="1" style="38" min="5" max="5"/>
+    <col width="10" customWidth="1" style="38" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1">
-      <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="9"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" s="10"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" ht="0.05" customHeight="1">
-      <c r="A3" s="10"/>
-      <c r="B3" t="s" s="13">
-        <v>0</v>
-      </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="12"/>
-    </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12"/>
-    </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12"/>
-    </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12"/>
+    <row r="1" ht="13.55" customHeight="1" s="51">
+      <c r="A1" s="7" t="n"/>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="13.55" customHeight="1" s="51">
+      <c r="A2" s="10" t="n"/>
+      <c r="B2" s="11" t="n"/>
+      <c r="C2" s="11" t="n"/>
+      <c r="D2" s="11" t="n"/>
+      <c r="E2" s="12" t="n"/>
+    </row>
+    <row r="3" ht="0.05" customHeight="1" s="51">
+      <c r="A3" s="10" t="n"/>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n"/>
+    </row>
+    <row r="4" ht="13.55" customHeight="1" s="51">
+      <c r="A4" s="10" t="n"/>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="12" t="n"/>
+    </row>
+    <row r="5" ht="13.55" customHeight="1" s="51">
+      <c r="A5" s="10" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="13.55" customHeight="1" s="51">
+      <c r="A6" s="10" t="n"/>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="12" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10"/>
-      <c r="B7" t="s" s="14">
-        <v>1</v>
-      </c>
-      <c r="C7" t="s" s="14">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s" s="14">
-        <v>3</v>
-      </c>
-      <c r="E7" s="12"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="12"/>
+      <c r="A7" s="10" t="n"/>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Numbers Sheet Name</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>Numbers Table Name</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Excel Worksheet Name</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n"/>
+    </row>
+    <row r="8" ht="13.55" customHeight="1" s="51">
+      <c r="A8" s="10" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10"/>
-      <c r="B9" t="s" s="15">
-        <v>6</v>
-      </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="12"/>
+      <c r="A9" s="10" t="n"/>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>BL Input</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="12" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10"/>
-      <c r="B10" s="17"/>
-      <c r="C10" t="s" s="18">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s" s="19">
-        <v>7</v>
-      </c>
-      <c r="E10" s="12"/>
-    </row>
-    <row r="11" ht="13" customHeight="1">
-      <c r="A11" s="10"/>
-      <c r="B11" t="s" s="3">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="12"/>
-    </row>
-    <row r="12" ht="13" customHeight="1">
-      <c r="A12" s="20"/>
-      <c r="B12" s="4"/>
-      <c r="C12" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s" s="5">
-        <v>6</v>
-      </c>
-      <c r="E12" s="21"/>
-    </row>
-    <row r="13" ht="13" customHeight="1">
-      <c r="A13" s="7"/>
-      <c r="B13" t="s" s="3">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="9"/>
-    </row>
-    <row r="14" ht="13" customHeight="1">
-      <c r="A14" s="20"/>
-      <c r="B14" s="4"/>
-      <c r="C14" t="s" s="4">
-        <v>5</v>
-      </c>
-      <c r="D14" t="s" s="5">
-        <v>8</v>
-      </c>
-      <c r="E14" s="21"/>
+      <c r="A10" s="10" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>BL Input</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="13" customHeight="1" s="51">
+      <c r="A11" s="10" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>BL Input</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="12" t="n"/>
+    </row>
+    <row r="12" ht="13" customHeight="1" s="51">
+      <c r="A12" s="20" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>BL Input</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n"/>
+    </row>
+    <row r="13" ht="13" customHeight="1" s="51">
+      <c r="A13" s="7" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Tracking Results</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="9" t="n"/>
+    </row>
+    <row r="14" ht="13" customHeight="1" s="51">
+      <c r="A14" s="20" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Tracking Results</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B3:D3"/>
+  <mergeCells count="1">
     <mergeCell ref="B3:D3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D10" location="'Export Summary'!R1C1" tooltip="" display="Export Summary"/>
     <hyperlink ref="D10" location="'BL Input'!R1C1" tooltip="" display="BL Input"/>
-    <hyperlink ref="D12" location="'BL Input'!R1C1" tooltip="" display="BL Input"/>
-    <hyperlink ref="D14" location="'Tracking Results'!R1C1" tooltip="" display="Tracking Results"/>
     <hyperlink ref="D12" location="'BL Input'!R1C1" tooltip="" display="BL Input"/>
     <hyperlink ref="D14" location="'Tracking Results'!R1C1" tooltip="" display="Tracking Results"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="16.5" style="25" customWidth="1"/>
-    <col min="2" max="2" width="24" style="25" customWidth="1"/>
-    <col min="3" max="5" width="8.85156" style="25" customWidth="1"/>
-    <col min="6" max="16384" width="8.85156" style="25" customWidth="1"/>
+    <col width="21.1719" customWidth="1" style="38" min="1" max="1"/>
+    <col width="24" customWidth="1" style="38" min="2" max="2"/>
+    <col width="8.851559999999999" customWidth="1" style="38" min="3" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="38" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" t="s" s="26">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s" s="26">
-        <v>11</v>
-      </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-    </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" t="s" s="29">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s" s="30">
-        <v>13</v>
-      </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-    </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" t="s" s="31">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s" s="32">
-        <v>13</v>
-      </c>
-      <c r="C3" s="33"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
-    </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" t="s" s="31">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s" s="32">
-        <v>13</v>
-      </c>
-      <c r="C4" s="33"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="35"/>
-    </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" t="s" s="31">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s" s="32">
-        <v>13</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="35"/>
-    </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" t="s" s="31">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s" s="32">
-        <v>13</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" t="s" s="31">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s" s="32">
-        <v>13</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="35"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" t="s" s="31">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s" s="36">
-        <v>13</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" t="s" s="31">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s" s="36">
-        <v>13</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12"/>
-    </row>
-    <row r="10" ht="13.55" customHeight="1">
-      <c r="A10" s="20"/>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="21"/>
+    <row r="1" ht="22" customHeight="1" s="51">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>BL No</t>
+        </is>
+      </c>
+      <c r="B1" s="26" t="inlineStr">
+        <is>
+          <t>Shipping Line</t>
+        </is>
+      </c>
+      <c r="C1" s="27" t="n"/>
+      <c r="D1" s="28" t="n"/>
+      <c r="E1" s="28" t="n"/>
+    </row>
+    <row r="2" ht="13.55" customHeight="1" s="51">
+      <c r="A2" s="29" t="inlineStr">
+        <is>
+          <t>KMTCSIN3292768</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>KMTC</t>
+        </is>
+      </c>
+      <c r="C2" s="31" t="n"/>
+      <c r="D2" s="32" t="n"/>
+      <c r="E2" s="33" t="n"/>
+    </row>
+    <row r="3" ht="16.65" customHeight="1" s="51">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>KMTCSIN3293757</t>
+        </is>
+      </c>
+      <c r="B3" s="35" t="inlineStr">
+        <is>
+          <t>KMTC</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="n"/>
+      <c r="D3" s="32" t="n"/>
+      <c r="E3" s="33" t="n"/>
+    </row>
+    <row r="4" ht="13.55" customHeight="1" s="51">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>KMTCSIN3292768</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="inlineStr">
+        <is>
+          <t>KMTC</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="9" t="n"/>
+    </row>
+    <row r="5" ht="13.55" customHeight="1" s="51">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>KMTCSIN3293757</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>KMTC</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="12" t="n"/>
+    </row>
+    <row r="6" ht="13.55" customHeight="1" s="51">
+      <c r="A6" s="20" t="n"/>
+      <c r="B6" s="37" t="n"/>
+      <c r="C6" s="37" t="n"/>
+      <c r="D6" s="37" t="n"/>
+      <c r="E6" s="21" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col min="1" max="1" width="18" style="38" customWidth="1"/>
-    <col min="2" max="2" width="15" style="38" customWidth="1"/>
-    <col min="3" max="4" width="20" style="38" customWidth="1"/>
-    <col min="5" max="5" width="18" style="38" customWidth="1"/>
-    <col min="6" max="6" width="22" style="38" customWidth="1"/>
-    <col min="7" max="8" width="20" style="38" customWidth="1"/>
-    <col min="9" max="9" width="28" style="38" customWidth="1"/>
-    <col min="10" max="10" width="18" style="38" customWidth="1"/>
-    <col min="11" max="16384" width="8.85156" style="38" customWidth="1"/>
+    <col width="18" customWidth="1" style="38" min="1" max="1"/>
+    <col width="15" customWidth="1" style="38" min="2" max="2"/>
+    <col width="20" customWidth="1" style="38" min="3" max="4"/>
+    <col width="20" customWidth="1" style="51" min="4" max="4"/>
+    <col width="18" customWidth="1" style="38" min="5" max="5"/>
+    <col width="22" customWidth="1" style="38" min="6" max="6"/>
+    <col width="20" customWidth="1" style="38" min="7" max="8"/>
+    <col width="20" customWidth="1" style="51" min="8" max="8"/>
+    <col width="28" customWidth="1" style="38" min="9" max="9"/>
+    <col width="18" customWidth="1" style="38" min="10" max="10"/>
+    <col width="8.851559999999999" customWidth="1" style="38" min="11" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" t="s" s="39">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s" s="39">
-        <v>11</v>
-      </c>
-      <c r="C1" t="s" s="39">
-        <v>21</v>
-      </c>
-      <c r="D1" t="s" s="39">
-        <v>22</v>
-      </c>
-      <c r="E1" t="s" s="39">
-        <v>23</v>
-      </c>
-      <c r="F1" t="s" s="39">
-        <v>24</v>
-      </c>
-      <c r="G1" t="s" s="39">
-        <v>25</v>
-      </c>
-      <c r="H1" t="s" s="39">
-        <v>26</v>
-      </c>
-      <c r="I1" t="s" s="39">
-        <v>27</v>
-      </c>
-      <c r="J1" s="40"/>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" t="s" s="41">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s" s="41">
-        <v>29</v>
-      </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" t="s" s="43">
-        <v>30</v>
-      </c>
-      <c r="F2" t="s" s="43">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s" s="43">
-        <v>32</v>
-      </c>
-      <c r="H2" t="s" s="44">
-        <v>33</v>
-      </c>
-      <c r="I2" t="s" s="45">
-        <v>34</v>
-      </c>
-      <c r="J2" t="s" s="43">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" t="s" s="46">
-        <v>36</v>
-      </c>
-      <c r="B3" t="s" s="46">
-        <v>29</v>
-      </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48"/>
-      <c r="F3" t="s" s="48">
-        <v>37</v>
-      </c>
-      <c r="G3" t="s" s="48">
-        <v>32</v>
-      </c>
-      <c r="H3" t="s" s="48">
-        <v>38</v>
-      </c>
-      <c r="I3" t="s" s="45">
-        <v>34</v>
-      </c>
-      <c r="J3" t="s" s="48">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" t="s" s="46">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s" s="46">
-        <v>29</v>
-      </c>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" t="s" s="48">
-        <v>40</v>
-      </c>
-      <c r="F4" t="s" s="48">
-        <v>41</v>
-      </c>
-      <c r="G4" t="s" s="48">
-        <v>42</v>
-      </c>
-      <c r="H4" t="s" s="48">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s" s="49">
-        <v>44</v>
-      </c>
-      <c r="J4" t="s" s="48">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" t="s" s="46">
-        <v>46</v>
-      </c>
-      <c r="B5" t="s" s="46">
-        <v>29</v>
-      </c>
-      <c r="C5" s="47"/>
-      <c r="D5" s="47"/>
-      <c r="E5" t="s" s="48">
-        <v>47</v>
-      </c>
-      <c r="F5" t="s" s="48">
-        <v>48</v>
-      </c>
-      <c r="G5" t="s" s="48">
-        <v>49</v>
-      </c>
-      <c r="H5" t="s" s="48">
-        <v>50</v>
-      </c>
-      <c r="I5" t="s" s="45">
-        <v>51</v>
-      </c>
-      <c r="J5" t="s" s="48">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" t="s" s="41">
-        <v>53</v>
-      </c>
-      <c r="B6" t="s" s="41">
-        <v>29</v>
-      </c>
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" t="s" s="43">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s" s="43">
-        <v>55</v>
-      </c>
-      <c r="G6" t="s" s="43">
-        <v>56</v>
-      </c>
-      <c r="H6" t="s" s="43">
-        <v>57</v>
-      </c>
-      <c r="I6" s="50"/>
-      <c r="J6" t="s" s="43">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" t="s" s="46">
-        <v>58</v>
-      </c>
-      <c r="B7" t="s" s="46">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s" s="48">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s" s="48">
-        <v>61</v>
-      </c>
-      <c r="E7" t="s" s="48">
-        <v>62</v>
-      </c>
-      <c r="F7" t="s" s="48">
-        <v>63</v>
-      </c>
-      <c r="G7" s="47"/>
-      <c r="H7" s="47"/>
-      <c r="I7" t="s" s="45">
-        <v>64</v>
-      </c>
-      <c r="J7" t="s" s="48">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" t="s" s="46">
-        <v>66</v>
-      </c>
-      <c r="B8" t="s" s="46">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s" s="48">
-        <v>67</v>
-      </c>
-      <c r="D8" t="s" s="48">
-        <v>68</v>
-      </c>
-      <c r="E8" t="s" s="48">
-        <v>69</v>
-      </c>
-      <c r="F8" t="s" s="48">
-        <v>63</v>
-      </c>
-      <c r="G8" s="47"/>
-      <c r="H8" s="47"/>
-      <c r="I8" t="s" s="45">
-        <v>70</v>
-      </c>
-      <c r="J8" t="s" s="48">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" t="s" s="41">
-        <v>72</v>
-      </c>
-      <c r="B9" t="s" s="41">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s" s="43">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s" s="43">
-        <v>74</v>
-      </c>
-      <c r="E9" t="s" s="43">
-        <v>75</v>
-      </c>
-      <c r="F9" t="s" s="43">
-        <v>76</v>
-      </c>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" t="s" s="45">
-        <v>77</v>
-      </c>
-      <c r="J9" t="s" s="43">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" t="s" s="46">
-        <v>78</v>
-      </c>
-      <c r="B10" t="s" s="46">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s" s="48">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s" s="48">
-        <v>74</v>
-      </c>
-      <c r="E10" t="s" s="48">
-        <v>80</v>
-      </c>
-      <c r="F10" t="s" s="48">
-        <v>81</v>
-      </c>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" t="s" s="49">
-        <v>82</v>
-      </c>
-      <c r="J10" t="s" s="48">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" t="s" s="41">
-        <v>83</v>
-      </c>
-      <c r="B11" t="s" s="41">
-        <v>59</v>
-      </c>
-      <c r="C11" t="s" s="43">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s" s="43">
-        <v>74</v>
-      </c>
-      <c r="E11" t="s" s="43">
-        <v>84</v>
-      </c>
-      <c r="F11" t="s" s="43">
-        <v>76</v>
-      </c>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" t="s" s="45">
-        <v>77</v>
-      </c>
-      <c r="J11" t="s" s="43">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" t="s" s="46">
-        <v>85</v>
-      </c>
-      <c r="B12" t="s" s="46">
-        <v>59</v>
-      </c>
-      <c r="C12" t="s" s="48">
-        <v>73</v>
-      </c>
-      <c r="D12" t="s" s="48">
-        <v>74</v>
-      </c>
-      <c r="E12" t="s" s="48">
-        <v>86</v>
-      </c>
-      <c r="F12" t="s" s="48">
-        <v>63</v>
-      </c>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" t="s" s="45">
-        <v>87</v>
-      </c>
-      <c r="J12" t="s" s="48">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" t="s" s="41">
-        <v>89</v>
-      </c>
-      <c r="B13" t="s" s="41">
-        <v>90</v>
-      </c>
-      <c r="C13" t="s" s="43">
-        <v>91</v>
-      </c>
-      <c r="D13" t="s" s="43">
-        <v>92</v>
-      </c>
-      <c r="E13" t="s" s="43">
-        <v>93</v>
-      </c>
-      <c r="F13" s="42"/>
-      <c r="G13" t="s" s="43">
-        <v>94</v>
-      </c>
-      <c r="H13" s="42"/>
-      <c r="I13" t="s" s="45">
-        <v>95</v>
-      </c>
-      <c r="J13" t="s" s="43">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" t="s" s="46">
-        <v>97</v>
-      </c>
-      <c r="B14" t="s" s="46">
-        <v>90</v>
-      </c>
-      <c r="C14" t="s" s="48">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s" s="48">
-        <v>99</v>
-      </c>
-      <c r="E14" t="s" s="48">
-        <v>100</v>
-      </c>
-      <c r="F14" s="47"/>
-      <c r="G14" t="s" s="48">
-        <v>101</v>
-      </c>
-      <c r="H14" s="47"/>
-      <c r="I14" t="s" s="45">
-        <v>102</v>
-      </c>
-      <c r="J14" t="s" s="48">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" t="s" s="41">
-        <v>104</v>
-      </c>
-      <c r="B15" t="s" s="41">
-        <v>90</v>
-      </c>
-      <c r="C15" t="s" s="43">
-        <v>105</v>
-      </c>
-      <c r="D15" t="s" s="43">
-        <v>106</v>
-      </c>
-      <c r="E15" t="s" s="43">
-        <v>107</v>
-      </c>
-      <c r="F15" s="42"/>
-      <c r="G15" t="s" s="43">
-        <v>108</v>
-      </c>
-      <c r="H15" s="42"/>
-      <c r="I15" t="s" s="45">
-        <v>109</v>
-      </c>
-      <c r="J15" t="s" s="43">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" t="s" s="46">
-        <v>110</v>
-      </c>
-      <c r="B16" t="s" s="46">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s" s="48">
-        <v>111</v>
-      </c>
-      <c r="D16" t="s" s="48">
-        <v>99</v>
-      </c>
-      <c r="E16" t="s" s="48">
-        <v>112</v>
-      </c>
-      <c r="F16" s="47"/>
-      <c r="G16" t="s" s="48">
-        <v>113</v>
-      </c>
-      <c r="H16" s="47"/>
-      <c r="I16" t="s" s="45">
-        <v>114</v>
-      </c>
-      <c r="J16" t="s" s="48">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" t="s" s="41">
-        <v>12</v>
-      </c>
-      <c r="B17" t="s" s="41">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s" s="43">
-        <v>116</v>
-      </c>
-      <c r="D17" t="s" s="43">
-        <v>117</v>
-      </c>
-      <c r="E17" t="s" s="43">
-        <v>118</v>
-      </c>
-      <c r="F17" s="42"/>
-      <c r="G17" t="s" s="43">
-        <v>119</v>
-      </c>
-      <c r="H17" s="42"/>
-      <c r="I17" t="s" s="45">
-        <v>120</v>
-      </c>
-      <c r="J17" t="s" s="43">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" t="s" s="46">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s" s="46">
-        <v>13</v>
-      </c>
-      <c r="C18" t="s" s="48">
-        <v>116</v>
-      </c>
-      <c r="D18" t="s" s="48">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s" s="48">
-        <v>122</v>
-      </c>
-      <c r="F18" s="47"/>
-      <c r="G18" t="s" s="48">
-        <v>123</v>
-      </c>
-      <c r="H18" s="47"/>
-      <c r="I18" t="s" s="45">
-        <v>120</v>
-      </c>
-      <c r="J18" t="s" s="48">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" t="s" s="41">
-        <v>17</v>
-      </c>
-      <c r="B19" t="s" s="41">
-        <v>13</v>
-      </c>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" t="s" s="43">
-        <v>125</v>
-      </c>
-      <c r="F19" s="42"/>
-      <c r="G19" s="42"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="50"/>
-      <c r="J19" t="s" s="43">
-        <v>126</v>
+    <row r="1" ht="22" customHeight="1" s="51">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>BL No</t>
+        </is>
+      </c>
+      <c r="B1" s="39" t="inlineStr">
+        <is>
+          <t>Shipping Line</t>
+        </is>
+      </c>
+      <c r="C1" s="39" t="inlineStr">
+        <is>
+          <t>POL</t>
+        </is>
+      </c>
+      <c r="D1" s="39" t="inlineStr">
+        <is>
+          <t>POD</t>
+        </is>
+      </c>
+      <c r="E1" s="39" t="inlineStr">
+        <is>
+          <t>Container No</t>
+        </is>
+      </c>
+      <c r="F1" s="39" t="inlineStr">
+        <is>
+          <t>Vessel</t>
+        </is>
+      </c>
+      <c r="G1" s="39" t="inlineStr">
+        <is>
+          <t>ATA</t>
+        </is>
+      </c>
+      <c r="H1" s="39" t="inlineStr">
+        <is>
+          <t>Latest Status</t>
+        </is>
+      </c>
+      <c r="I1" s="39" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
+      </c>
+      <c r="J1" s="40" t="n"/>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="51">
+      <c r="A2" s="41" t="inlineStr">
+        <is>
+          <t>6439251269</t>
+        </is>
+      </c>
+      <c r="B2" s="41" t="inlineStr">
+        <is>
+          <t>Cosco</t>
+        </is>
+      </c>
+      <c r="C2" s="42" t="n"/>
+      <c r="D2" s="42" t="n"/>
+      <c r="E2" s="43" t="inlineStr">
+        <is>
+          <t>CSNU6515981</t>
+        </is>
+      </c>
+      <c r="F2" s="43" t="inlineStr">
+        <is>
+          <t>EVER ACME</t>
+        </is>
+      </c>
+      <c r="G2" s="43" t="inlineStr">
+        <is>
+          <t>2026-03-06 06:00:00 IST</t>
+        </is>
+      </c>
+      <c r="H2" s="44" t="inlineStr">
+        <is>
+          <t>2026-03-08 15:20:00 IST</t>
+        </is>
+      </c>
+      <c r="I2" s="45" t="inlineStr">
+        <is>
+          <t>Transport Completed</t>
+        </is>
+      </c>
+      <c r="J2" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="51">
+      <c r="A3" s="46" t="inlineStr">
+        <is>
+          <t>6439658390</t>
+        </is>
+      </c>
+      <c r="B3" s="46" t="inlineStr">
+        <is>
+          <t>Cosco</t>
+        </is>
+      </c>
+      <c r="C3" s="47" t="n"/>
+      <c r="D3" s="47" t="n"/>
+      <c r="E3" s="48" t="n"/>
+      <c r="F3" s="48" t="inlineStr">
+        <is>
+          <t>No data</t>
+        </is>
+      </c>
+      <c r="G3" s="48" t="inlineStr">
+        <is>
+          <t>2026-03-06 06:00:00 IST</t>
+        </is>
+      </c>
+      <c r="H3" s="48" t="inlineStr">
+        <is>
+          <t>2026-03-08 06:33:00 IST</t>
+        </is>
+      </c>
+      <c r="I3" s="45" t="inlineStr">
+        <is>
+          <t>Transport Completed</t>
+        </is>
+      </c>
+      <c r="J3" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="51">
+      <c r="A4" s="46" t="inlineStr">
+        <is>
+          <t>6449537710</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="inlineStr">
+        <is>
+          <t>Cosco</t>
+        </is>
+      </c>
+      <c r="C4" s="47" t="n"/>
+      <c r="D4" s="47" t="n"/>
+      <c r="E4" s="48" t="inlineStr">
+        <is>
+          <t>CSGU6346619</t>
+        </is>
+      </c>
+      <c r="F4" s="48" t="inlineStr">
+        <is>
+          <t>TEXAS TRIUMPH</t>
+        </is>
+      </c>
+      <c r="G4" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-28 03:30:00 IST</t>
+        </is>
+      </c>
+      <c r="H4" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-29 04:43:00 IST</t>
+        </is>
+      </c>
+      <c r="I4" s="49" t="inlineStr">
+        <is>
+          <t>Empty Return</t>
+        </is>
+      </c>
+      <c r="J4" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="51">
+      <c r="A5" s="46" t="inlineStr">
+        <is>
+          <t>6450334910</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="inlineStr">
+        <is>
+          <t>Cosco</t>
+        </is>
+      </c>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="48" t="inlineStr">
+        <is>
+          <t>CSGU6674264</t>
+        </is>
+      </c>
+      <c r="F5" s="48" t="inlineStr">
+        <is>
+          <t>UAFL RACER</t>
+        </is>
+      </c>
+      <c r="G5" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-30 20:00:00 IST</t>
+        </is>
+      </c>
+      <c r="H5" s="48" t="inlineStr">
+        <is>
+          <t>2026-07-04 00:00:00 IST</t>
+        </is>
+      </c>
+      <c r="I5" s="45" t="inlineStr">
+        <is>
+          <t>Discharged at T/S Port</t>
+        </is>
+      </c>
+      <c r="J5" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="51">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>6500092990</t>
+        </is>
+      </c>
+      <c r="B6" s="41" t="inlineStr">
+        <is>
+          <t>Cosco</t>
+        </is>
+      </c>
+      <c r="C6" s="42" t="n"/>
+      <c r="D6" s="42" t="n"/>
+      <c r="E6" s="43" t="inlineStr">
+        <is>
+          <t>BEAU5564910</t>
+        </is>
+      </c>
+      <c r="F6" s="43" t="inlineStr">
+        <is>
+          <t>CMA CGM COLUMBIA</t>
+        </is>
+      </c>
+      <c r="G6" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-19 12:30:00 IST</t>
+        </is>
+      </c>
+      <c r="H6" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-20 00:00:00 IST</t>
+        </is>
+      </c>
+      <c r="I6" s="50" t="n"/>
+      <c r="J6" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-03 12:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="51">
+      <c r="A7" s="46" t="inlineStr">
+        <is>
+          <t>268533123</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="inlineStr">
+        <is>
+          <t>MAERSK</t>
+        </is>
+      </c>
+      <c r="C7" s="48" t="inlineStr">
+        <is>
+          <t>BARCELONA</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>JAWAHARLAL NEHRU</t>
+        </is>
+      </c>
+      <c r="E7" s="48" t="inlineStr">
+        <is>
+          <t>CAAU5397306</t>
+        </is>
+      </c>
+      <c r="F7" s="48" t="inlineStr">
+        <is>
+          <t>Discharge</t>
+        </is>
+      </c>
+      <c r="G7" s="47" t="n"/>
+      <c r="H7" s="47" t="n"/>
+      <c r="I7" s="45" t="inlineStr">
+        <is>
+          <t>Discharge • COLOMBO, SRI LANKA • 27 May 2026</t>
+        </is>
+      </c>
+      <c r="J7" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="51">
+      <c r="A8" s="46" t="inlineStr">
+        <is>
+          <t>269381946</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="inlineStr">
+        <is>
+          <t>MAERSK</t>
+        </is>
+      </c>
+      <c r="C8" s="48" t="inlineStr">
+        <is>
+          <t>ZAGREB</t>
+        </is>
+      </c>
+      <c r="D8" s="48" t="inlineStr">
+        <is>
+          <t>HAZIRA</t>
+        </is>
+      </c>
+      <c r="E8" s="48" t="inlineStr">
+        <is>
+          <t>MRKU4225082</t>
+        </is>
+      </c>
+      <c r="F8" s="48" t="inlineStr">
+        <is>
+          <t>Discharge</t>
+        </is>
+      </c>
+      <c r="G8" s="47" t="n"/>
+      <c r="H8" s="47" t="n"/>
+      <c r="I8" s="45" t="inlineStr">
+        <is>
+          <t>Discharge • PORT TANGIER MEDITERRANEE, MOROCCO • 16 May 2026</t>
+        </is>
+      </c>
+      <c r="J8" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="51">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>269383957</t>
+        </is>
+      </c>
+      <c r="B9" s="41" t="inlineStr">
+        <is>
+          <t>MAERSK</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>DURBAN</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>TUTICORIN</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>FFAU2279258</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
+        <is>
+          <t>Vessel departure</t>
+        </is>
+      </c>
+      <c r="G9" s="42" t="n"/>
+      <c r="H9" s="42" t="n"/>
+      <c r="I9" s="45" t="inlineStr">
+        <is>
+          <t>Vessel departure • MUNDRA, INDIA • 31 May 2026</t>
+        </is>
+      </c>
+      <c r="J9" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="51">
+      <c r="A10" s="46" t="inlineStr">
+        <is>
+          <t>267399967</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="inlineStr">
+        <is>
+          <t>MAERSK</t>
+        </is>
+      </c>
+      <c r="C10" s="48" t="inlineStr">
+        <is>
+          <t>ASHDOD</t>
+        </is>
+      </c>
+      <c r="D10" s="48" t="inlineStr">
+        <is>
+          <t>TUTICORIN</t>
+        </is>
+      </c>
+      <c r="E10" s="48" t="inlineStr">
+        <is>
+          <t>GAOU7118850</t>
+        </is>
+      </c>
+      <c r="F10" s="48" t="inlineStr">
+        <is>
+          <t>Empty container return</t>
+        </is>
+      </c>
+      <c r="G10" s="47" t="n"/>
+      <c r="H10" s="47" t="n"/>
+      <c r="I10" s="49" t="inlineStr">
+        <is>
+          <t>Empty container return • Tuticorin, India • 22 May 2026</t>
+        </is>
+      </c>
+      <c r="J10" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="51">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>269234530</t>
+        </is>
+      </c>
+      <c r="B11" s="41" t="inlineStr">
+        <is>
+          <t>MAERSK</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>DURBAN</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>TUTICORIN</t>
+        </is>
+      </c>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>TLLU5276111</t>
+        </is>
+      </c>
+      <c r="F11" s="43" t="inlineStr">
+        <is>
+          <t>Vessel departure</t>
+        </is>
+      </c>
+      <c r="G11" s="42" t="n"/>
+      <c r="H11" s="42" t="n"/>
+      <c r="I11" s="45" t="inlineStr">
+        <is>
+          <t>Vessel departure • MUNDRA, INDIA • 31 May 2026</t>
+        </is>
+      </c>
+      <c r="J11" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="51">
+      <c r="A12" s="46" t="inlineStr">
+        <is>
+          <t>269234219</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="inlineStr">
+        <is>
+          <t>MAERSK</t>
+        </is>
+      </c>
+      <c r="C12" s="48" t="inlineStr">
+        <is>
+          <t>DURBAN</t>
+        </is>
+      </c>
+      <c r="D12" s="48" t="inlineStr">
+        <is>
+          <t>TUTICORIN</t>
+        </is>
+      </c>
+      <c r="E12" s="48" t="inlineStr">
+        <is>
+          <t>MRSU4482165</t>
+        </is>
+      </c>
+      <c r="F12" s="48" t="inlineStr">
+        <is>
+          <t>Discharge</t>
+        </is>
+      </c>
+      <c r="G12" s="47" t="n"/>
+      <c r="H12" s="47" t="n"/>
+      <c r="I12" s="45" t="inlineStr">
+        <is>
+          <t>Discharge • MUNDRA, INDIA • 12 May 2026</t>
+        </is>
+      </c>
+      <c r="J12" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 14:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="51">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>MEDUGR867656</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="C13" s="43" t="inlineStr">
+        <is>
+          <t>Sydney, AU</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>Tuticorin, IN</t>
+        </is>
+      </c>
+      <c r="E13" s="43" t="inlineStr">
+        <is>
+          <t>FFAU2577550</t>
+        </is>
+      </c>
+      <c r="F13" s="42" t="n"/>
+      <c r="G13" s="43" t="inlineStr">
+        <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="H13" s="42" t="n"/>
+      <c r="I13" s="45" t="inlineStr">
+        <is>
+          <t>Import Positioning In • Tuticorin, IN • 22/05/2026</t>
+        </is>
+      </c>
+      <c r="J13" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="51">
+      <c r="A14" s="46" t="inlineStr">
+        <is>
+          <t>MEDURE451006</t>
+        </is>
+      </c>
+      <c r="B14" s="46" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="C14" s="48" t="inlineStr">
+        <is>
+          <t>Liverpool, GB</t>
+        </is>
+      </c>
+      <c r="D14" s="48" t="inlineStr">
+        <is>
+          <t>Hazira Port/Surat, IN</t>
+        </is>
+      </c>
+      <c r="E14" s="48" t="inlineStr">
+        <is>
+          <t>MSBU6848060</t>
+        </is>
+      </c>
+      <c r="F14" s="47" t="n"/>
+      <c r="G14" s="48" t="inlineStr">
+        <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="H14" s="47" t="n"/>
+      <c r="I14" s="45" t="inlineStr">
+        <is>
+          <t>Empty received at CY • Hazira Port/Surat, IN • 02/06/2026</t>
+        </is>
+      </c>
+      <c r="J14" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="51">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>MEDUBF405808</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="inlineStr">
+        <is>
+          <t>Belfast, GB</t>
+        </is>
+      </c>
+      <c r="D15" s="43" t="inlineStr">
+        <is>
+          <t>Nhava Sheva, IN</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>MSDU7055448</t>
+        </is>
+      </c>
+      <c r="F15" s="42" t="n"/>
+      <c r="G15" s="43" t="inlineStr">
+        <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="H15" s="42" t="n"/>
+      <c r="I15" s="45" t="inlineStr">
+        <is>
+          <t>Empty received at CY • Nhava Sheva, IN • 11/05/2026</t>
+        </is>
+      </c>
+      <c r="J15" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="51">
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>MEDUK9740334</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>MSC</t>
+        </is>
+      </c>
+      <c r="C16" s="48" t="inlineStr">
+        <is>
+          <t>Gioia Tauro, IT</t>
+        </is>
+      </c>
+      <c r="D16" s="48" t="inlineStr">
+        <is>
+          <t>Hazira Port/Surat, IN</t>
+        </is>
+      </c>
+      <c r="E16" s="48" t="inlineStr">
+        <is>
+          <t>CAIU7128171</t>
+        </is>
+      </c>
+      <c r="F16" s="47" t="n"/>
+      <c r="G16" s="48" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="H16" s="47" t="n"/>
+      <c r="I16" s="45" t="inlineStr">
+        <is>
+          <t>Empty received at CY • Hazira Port/Surat, IN • 31/03/2026</t>
+        </is>
+      </c>
+      <c r="J16" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="51">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>LPL1488455</t>
+        </is>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>FELIXSTOWE (GB)</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>TUTICORIN (IN)</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>CMAU8991493</t>
+        </is>
+      </c>
+      <c r="F17" s="42" t="n"/>
+      <c r="G17" s="43" t="inlineStr">
+        <is>
+          <t>Monday, 16-MAR-2026 12:21 PM</t>
+        </is>
+      </c>
+      <c r="H17" s="42" t="n"/>
+      <c r="I17" s="45" t="inlineStr">
+        <is>
+          <t>TUTICORIN
+CCIS GOLDEN HORN CONTAINER SERVICE</t>
+        </is>
+      </c>
+      <c r="J17" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="51">
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>LPL1489111</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C18" s="48" t="inlineStr">
+        <is>
+          <t>FELIXSTOWE (GB)</t>
+        </is>
+      </c>
+      <c r="D18" s="48" t="inlineStr">
+        <is>
+          <t>TUTICORIN (IN)</t>
+        </is>
+      </c>
+      <c r="E18" s="48" t="inlineStr">
+        <is>
+          <t>ECMU5181172</t>
+        </is>
+      </c>
+      <c r="F18" s="47" t="n"/>
+      <c r="G18" s="48" t="inlineStr">
+        <is>
+          <t>Wednesday, 01-APR-2026 11:01 PM</t>
+        </is>
+      </c>
+      <c r="H18" s="47" t="n"/>
+      <c r="I18" s="45" t="inlineStr">
+        <is>
+          <t>TUTICORIN
+CCIS GOLDEN HORN CONTAINER SERVICE</t>
+        </is>
+      </c>
+      <c r="J18" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="51">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>LPL1489079</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>CMA</t>
+        </is>
+      </c>
+      <c r="C19" s="42" t="n"/>
+      <c r="D19" s="42" t="n"/>
+      <c r="E19" s="43" t="inlineStr">
+        <is>
+          <t>ECMU5145663</t>
+        </is>
+      </c>
+      <c r="F19" s="42" t="n"/>
+      <c r="G19" s="42" t="n"/>
+      <c r="H19" s="42" t="n"/>
+      <c r="I19" s="50" t="n"/>
+      <c r="J19" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="51">
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>HLCULIV251113466</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>Hapag</t>
+        </is>
+      </c>
+      <c r="C20" s="47" t="n"/>
+      <c r="D20" s="48" t="inlineStr">
+        <is>
+          <t>TUTICORIN</t>
+        </is>
+      </c>
+      <c r="E20" s="48" t="inlineStr">
+        <is>
+          <t>HAMU3920481</t>
+        </is>
+      </c>
+      <c r="F20" s="48" t="inlineStr">
+        <is>
+          <t>2026-01-01 / 13:30</t>
+        </is>
+      </c>
+      <c r="G20" s="48" t="inlineStr">
+        <is>
+          <t>Discharged COLOMBO</t>
+        </is>
+      </c>
+      <c r="H20" s="47" t="n"/>
+      <c r="I20" s="45" t="inlineStr">
+        <is>
+          <t>Status Place of Activity Date Time Transport Voyage No.
+Discharged COLOMBO 2026-01-01 13:30 CAP SAN SOUNIO 601W
+Departure from COLOMBO 2026-01-01 20:26 Truck
+Arrival in COLOMBO 2026-01-01 20:50 Truck
+Loaded COLOMBO 2026-01-06 15:28 HE YUAN SHUN 89 014N
+Discharged TUTICORIN 2026-01-08 02:42 HE YUAN SHUN 89 014N
+Departure from TUTICORIN 2026-01-08 15:55 Truck
+Gate in empty TUTICORIN 2026-01-19 23:08 Truck</t>
+        </is>
+      </c>
+      <c r="J20" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="51">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>HLCUDUR260100370</t>
+        </is>
+      </c>
+      <c r="B21" s="41" t="inlineStr">
+        <is>
+          <t>Hapag</t>
+        </is>
+      </c>
+      <c r="C21" s="42" t="n"/>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>HAZIRA</t>
+        </is>
+      </c>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>FANU3793115</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="inlineStr">
+        <is>
+          <t>2026-01-05 / 07:15</t>
+        </is>
+      </c>
+      <c r="G21" s="43" t="inlineStr">
+        <is>
+          <t>Gate out empty DURBAN</t>
+        </is>
+      </c>
+      <c r="H21" s="42" t="n"/>
+      <c r="I21" s="49" t="inlineStr">
+        <is>
+          <t>Status Place of Activity Date Time Transport Voyage No.
+Gate out empty DURBAN 2026-01-05 07:15 Truck
+Arrival in DURBAN 2026-01-05 14:33 Truck
+Loaded DURBAN 2026-01-07 19:16 RIO GRANDE EXPRESS 2545E
+Discharged HAZIRA 2026-01-28 18:45 RIO GRANDE EXPRESS 2545E
+Departure from HAZIRA 2026-01-29 10:56 Truck
+Gate in empty HAZIRA 2026-02-05 07:42 Truck</t>
+        </is>
+      </c>
+      <c r="J21" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="51">
+      <c r="A22" s="46" t="inlineStr">
+        <is>
+          <t>A02GX00036</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>Interasia</t>
+        </is>
+      </c>
+      <c r="C22" s="47" t="n"/>
+      <c r="D22" s="47" t="n"/>
+      <c r="E22" s="48" t="inlineStr">
+        <is>
+          <t>IAAU1049817</t>
+        </is>
+      </c>
+      <c r="F22" s="47" t="n"/>
+      <c r="G22" s="48" t="inlineStr">
+        <is>
+          <t>2026/03/05 19:00:00</t>
+        </is>
+      </c>
+      <c r="H22" s="47" t="n"/>
+      <c r="I22" s="45" t="inlineStr">
+        <is>
+          <t>2026/03/05 19:00:00</t>
+        </is>
+      </c>
+      <c r="J22" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="51">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>A49GA00214</t>
+        </is>
+      </c>
+      <c r="B23" s="41" t="inlineStr">
+        <is>
+          <t>Interasia</t>
+        </is>
+      </c>
+      <c r="C23" s="42" t="n"/>
+      <c r="D23" s="42" t="n"/>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>DRYU9723739</t>
+        </is>
+      </c>
+      <c r="F23" s="42" t="n"/>
+      <c r="G23" s="43" t="inlineStr">
+        <is>
+          <t>2026/02/15 14:00:00</t>
+        </is>
+      </c>
+      <c r="H23" s="42" t="n"/>
+      <c r="I23" s="45" t="inlineStr">
+        <is>
+          <t>2026/02/15 14:00:00</t>
+        </is>
+      </c>
+      <c r="J23" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="51">
+      <c r="A24" s="46" t="inlineStr">
+        <is>
+          <t>A02GX00139</t>
+        </is>
+      </c>
+      <c r="B24" s="46" t="inlineStr">
+        <is>
+          <t>Interasia</t>
+        </is>
+      </c>
+      <c r="C24" s="47" t="n"/>
+      <c r="D24" s="47" t="n"/>
+      <c r="E24" s="48" t="inlineStr">
+        <is>
+          <t>BHCU5009391</t>
+        </is>
+      </c>
+      <c r="F24" s="47" t="n"/>
+      <c r="G24" s="48" t="inlineStr">
+        <is>
+          <t>2026/03/15 18:00:00</t>
+        </is>
+      </c>
+      <c r="H24" s="47" t="n"/>
+      <c r="I24" s="45" t="inlineStr">
+        <is>
+          <t>2026/03/15 18:00:00</t>
+        </is>
+      </c>
+      <c r="J24" s="48" t="inlineStr">
+        <is>
+          <t>2026-06-04 17:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="51">
+      <c r="A25" s="52" t="inlineStr">
+        <is>
+          <t>KMTCSIN3292768</t>
+        </is>
+      </c>
+      <c r="B25" s="52" t="inlineStr">
+        <is>
+          <t>KMTC</t>
+        </is>
+      </c>
+      <c r="C25" s="53" t="inlineStr"/>
+      <c r="D25" s="53" t="inlineStr"/>
+      <c r="E25" s="53" t="inlineStr"/>
+      <c r="F25" s="53" t="inlineStr"/>
+      <c r="G25" s="53" t="inlineStr"/>
+      <c r="H25" s="53" t="inlineStr"/>
+      <c r="I25" s="54" t="inlineStr">
+        <is>
+          <t>Error: Message: no such element: Unable to locate element: {"method":"css selector","se</t>
+        </is>
+      </c>
+      <c r="J25" s="53" t="inlineStr">
+        <is>
+          <t>2026-06-05 13:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="51">
+      <c r="A26" s="55" t="inlineStr">
+        <is>
+          <t>KMTCSIN3293757</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="inlineStr">
+        <is>
+          <t>KMTC</t>
+        </is>
+      </c>
+      <c r="C26" s="56" t="inlineStr"/>
+      <c r="D26" s="56" t="inlineStr"/>
+      <c r="E26" s="56" t="inlineStr"/>
+      <c r="F26" s="56" t="inlineStr"/>
+      <c r="G26" s="56" t="inlineStr"/>
+      <c r="H26" s="56" t="inlineStr"/>
+      <c r="I26" s="54" t="inlineStr">
+        <is>
+          <t>Error: Page did not load</t>
+        </is>
+      </c>
+      <c r="J26" s="56" t="inlineStr">
+        <is>
+          <t>2026-06-05 13:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="51">
+      <c r="A27" s="52" t="inlineStr">
+        <is>
+          <t>KMTCSIN3292768</t>
+        </is>
+      </c>
+      <c r="B27" s="52" t="inlineStr">
+        <is>
+          <t>KMTC</t>
+        </is>
+      </c>
+      <c r="C27" s="53" t="inlineStr"/>
+      <c r="D27" s="53" t="inlineStr"/>
+      <c r="E27" s="53" t="inlineStr"/>
+      <c r="F27" s="53" t="inlineStr"/>
+      <c r="G27" s="53" t="inlineStr"/>
+      <c r="H27" s="53" t="inlineStr"/>
+      <c r="I27" s="54" t="inlineStr">
+        <is>
+          <t>Error: Page did not load</t>
+        </is>
+      </c>
+      <c r="J27" s="53" t="inlineStr">
+        <is>
+          <t>2026-06-05 13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="51">
+      <c r="A28" s="55" t="inlineStr">
+        <is>
+          <t>KMTCSIN3293757</t>
+        </is>
+      </c>
+      <c r="B28" s="55" t="inlineStr">
+        <is>
+          <t>KMTC</t>
+        </is>
+      </c>
+      <c r="C28" s="56" t="inlineStr"/>
+      <c r="D28" s="56" t="inlineStr"/>
+      <c r="E28" s="56" t="inlineStr"/>
+      <c r="F28" s="56" t="inlineStr"/>
+      <c r="G28" s="56" t="inlineStr"/>
+      <c r="H28" s="56" t="inlineStr"/>
+      <c r="I28" s="54" t="inlineStr">
+        <is>
+          <t>Error: Page did not load</t>
+        </is>
+      </c>
+      <c r="J28" s="56" t="inlineStr">
+        <is>
+          <t>2026-06-05 13:10</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
   </headerFooter>
 </worksheet>
 </file>